--- a/output/graded_history/user_scorecards/2026-02-22.xlsx
+++ b/output/graded_history/user_scorecards/2026-02-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L164"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>31.53</v>
+        <v>31.3</v>
       </c>
       <c r="H3" t="n">
-        <v>0.788</v>
+        <v>0.777</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -605,17 +605,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.99</v>
+        <v>3.34</v>
       </c>
       <c r="H4" t="n">
-        <v>0.746</v>
+        <v>0.756</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -661,17 +661,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -688,10 +688,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>0.99</v>
       </c>
       <c r="H5" t="n">
-        <v>0.742</v>
+        <v>0.746</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -717,26 +717,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>25.5</v>
+        <v>3.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -744,14 +744,14 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30.44</v>
+        <v>2.53</v>
       </c>
       <c r="H6" t="n">
-        <v>0.742</v>
+        <v>0.737</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -800,10 +800,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5.46</v>
+        <v>5.57</v>
       </c>
       <c r="H7" t="n">
-        <v>0.739</v>
+        <v>0.731</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -829,26 +829,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3.47</v>
+        <v>2.55</v>
       </c>
       <c r="H8" t="n">
-        <v>0.73</v>
+        <v>0.729</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -885,26 +885,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.56</v>
+        <v>5.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0.728</v>
+        <v>0.716</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -941,26 +941,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -968,10 +968,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>4.99</v>
+        <v>6.64</v>
       </c>
       <c r="H10" t="n">
-        <v>0.719</v>
+        <v>0.713</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -997,26 +997,26 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8.5</v>
+        <v>33.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6.56</v>
+        <v>29.23</v>
       </c>
       <c r="H11" t="n">
-        <v>0.718</v>
+        <v>0.712</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12.91</v>
+        <v>12.76</v>
       </c>
       <c r="H12" t="n">
-        <v>0.718</v>
+        <v>0.705</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1109,26 +1109,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>19.5</v>
+        <v>25.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1136,14 +1136,14 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14.55</v>
+        <v>29.56</v>
       </c>
       <c r="H13" t="n">
-        <v>0.712</v>
+        <v>0.704</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1165,26 +1165,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>33.5</v>
+        <v>1.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>29.26</v>
+        <v>1.19</v>
       </c>
       <c r="H14" t="n">
-        <v>0.71</v>
+        <v>0.701</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19.35</v>
+        <v>19.53</v>
       </c>
       <c r="H15" t="n">
-        <v>0.707</v>
+        <v>0.699</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1277,26 +1277,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bub Carrington</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>15.51</v>
+        <v>6.35</v>
       </c>
       <c r="H16" t="n">
-        <v>0.704</v>
+        <v>0.695</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1333,26 +1333,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.19</v>
+        <v>2.83</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1389,22 +1389,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1445,26 +1445,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Joan Beringer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6.35</v>
+        <v>2.95</v>
       </c>
       <c r="H19" t="n">
-        <v>0.694</v>
+        <v>0.921</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1501,26 +1501,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.5</v>
+        <v>27.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2.83</v>
+        <v>23.23</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.769</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1557,7 +1557,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Joan Beringer</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.95</v>
+        <v>2.34</v>
       </c>
       <c r="H21" t="n">
-        <v>0.921</v>
+        <v>0.758</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1613,26 +1613,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Kyshawn George</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>27.5</v>
+        <v>12.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>22.68</v>
+        <v>8.75</v>
       </c>
       <c r="H22" t="n">
-        <v>0.796</v>
+        <v>0.743</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1669,17 +1669,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1688,7 +1688,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2.34</v>
+        <v>6.02</v>
       </c>
       <c r="H23" t="n">
-        <v>0.758</v>
+        <v>0.741</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1725,26 +1725,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kyshawn George</t>
+          <t>Payton Pritchard</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>12.5</v>
+        <v>27.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1752,14 +1752,14 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>8.640000000000001</v>
+        <v>33.61</v>
       </c>
       <c r="H24" t="n">
-        <v>0.749</v>
+        <v>0.724</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1781,26 +1781,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>5.99</v>
+        <v>1.84</v>
       </c>
       <c r="H25" t="n">
-        <v>0.746</v>
+        <v>0.72</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1864,10 +1864,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5.44</v>
+        <v>5.48</v>
       </c>
       <c r="H26" t="n">
-        <v>0.727</v>
+        <v>0.718</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1893,26 +1893,26 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>11.11</v>
+        <v>3.49</v>
       </c>
       <c r="H27" t="n">
-        <v>0.724</v>
+        <v>0.716</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1949,26 +1949,26 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3.45</v>
+        <v>11.29</v>
       </c>
       <c r="H28" t="n">
-        <v>0.722</v>
+        <v>0.713</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2005,26 +2005,26 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>23.89</v>
+        <v>1.87</v>
       </c>
       <c r="H29" t="n">
-        <v>0.72</v>
+        <v>0.711</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2061,26 +2061,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>OKC</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>AST</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.84</v>
+        <v>1.32</v>
       </c>
       <c r="H30" t="n">
-        <v>0.719</v>
+        <v>0.711</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2132,11 +2132,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2.5</v>
+        <v>27.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.87</v>
+        <v>24.09</v>
       </c>
       <c r="H31" t="n">
-        <v>0.715</v>
+        <v>0.709</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2173,17 +2173,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2200,10 +2200,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.34</v>
+        <v>2.05</v>
       </c>
       <c r="H32" t="n">
-        <v>0.705</v>
+        <v>0.698</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2229,17 +2229,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Egor Demin</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.04</v>
+        <v>2.92</v>
       </c>
       <c r="H33" t="n">
-        <v>0.701</v>
+        <v>0.665</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2285,26 +2285,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>8.5</v>
+        <v>17.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>7.16</v>
+        <v>15.96</v>
       </c>
       <c r="H34" t="n">
-        <v>0.681</v>
+        <v>0.661</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2341,26 +2341,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2368,14 +2368,14 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3.74</v>
+        <v>12.2</v>
       </c>
       <c r="H35" t="n">
-        <v>0.675</v>
+        <v>0.66</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2397,26 +2397,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Egor Demin</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2424,10 +2424,10 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2.96</v>
+        <v>3.86</v>
       </c>
       <c r="H36" t="n">
-        <v>0.655</v>
+        <v>0.654</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2453,26 +2453,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2480,10 +2480,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>12.14</v>
+        <v>3.35</v>
       </c>
       <c r="H37" t="n">
-        <v>0.655</v>
+        <v>0.65</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2509,17 +2509,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3.89</v>
+        <v>2.99</v>
       </c>
       <c r="H38" t="n">
-        <v>0.65</v>
+        <v>0.649</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2565,26 +2565,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>ORL</t>
-        </is>
-      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2592,14 +2592,14 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>3.34</v>
+        <v>13.15</v>
       </c>
       <c r="H39" t="n">
         <v>0.648</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2621,17 +2621,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>14.5</v>
+        <v>20.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>16.68</v>
+        <v>23.18</v>
       </c>
       <c r="H40" t="n">
-        <v>0.639</v>
+        <v>0.648</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2677,26 +2677,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>25.5</v>
+        <v>5.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2704,14 +2704,14 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>30.33</v>
+        <v>4.85</v>
       </c>
       <c r="H41" t="n">
-        <v>0.635</v>
+        <v>0.64</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2733,26 +2733,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Corey Kispert</t>
+          <t>Nolan Traore</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>13.5</v>
+        <v>4.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2760,14 +2760,14 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>11.56</v>
+        <v>6.02</v>
       </c>
       <c r="H42" t="n">
-        <v>0.633</v>
+        <v>0.64</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2816,10 +2816,10 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="H43" t="n">
-        <v>0.63</v>
+        <v>0.637</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2845,17 +2845,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Luka Doncic</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2872,10 +2872,10 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1.39</v>
+        <v>6.76</v>
       </c>
       <c r="H44" t="n">
-        <v>0.63</v>
+        <v>0.631</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2901,26 +2901,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>30.5</v>
+        <v>14.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2928,10 +2928,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>32.67</v>
+        <v>16.52</v>
       </c>
       <c r="H45" t="n">
-        <v>0.63</v>
+        <v>0.629</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2972,11 +2972,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2984,14 +2984,14 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>3.08</v>
+        <v>30.01</v>
       </c>
       <c r="H46" t="n">
-        <v>0.629</v>
+        <v>0.626</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3013,26 +3013,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nolan Traore</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3040,14 +3040,14 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>5.92</v>
+        <v>7.6</v>
       </c>
       <c r="H47" t="n">
-        <v>0.626</v>
+        <v>0.624</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3069,17 +3069,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2.26</v>
+        <v>1.41</v>
       </c>
       <c r="H48" t="n">
-        <v>0.621</v>
+        <v>0.623</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3125,26 +3125,26 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Kristaps Porzingis</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4.63</v>
+        <v>1.31</v>
       </c>
       <c r="H49" t="n">
         <v>0.68</v>
@@ -3181,17 +3181,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kristaps Porzingis</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H50" t="n">
-        <v>0.68</v>
+        <v>0.678</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3252,11 +3252,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>28.5</v>
+        <v>6.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>25.27</v>
+        <v>5.55</v>
       </c>
       <c r="H51" t="n">
         <v>0.678</v>
@@ -3293,26 +3293,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.32</v>
+        <v>4.59</v>
       </c>
       <c r="H52" t="n">
         <v>0.677</v>
@@ -3349,26 +3349,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
           <t>CHA</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>WAS</t>
-        </is>
-      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2.06</v>
+        <v>4.67</v>
       </c>
       <c r="H53" t="n">
         <v>0.674</v>
@@ -3405,17 +3405,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="H54" t="n">
-        <v>0.667</v>
+        <v>0.674</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3461,17 +3461,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3480,7 +3480,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3488,10 +3488,10 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3.82</v>
+        <v>3.02</v>
       </c>
       <c r="H55" t="n">
-        <v>0.664</v>
+        <v>0.667</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3517,26 +3517,26 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="H56" t="n">
         <v>0.663</v>
@@ -3573,26 +3573,26 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3600,14 +3600,14 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3.04</v>
+        <v>5.62</v>
       </c>
       <c r="H57" t="n">
-        <v>0.661</v>
+        <v>0.66</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3644,11 +3644,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4.5</v>
+        <v>16.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3.85</v>
+        <v>13.7</v>
       </c>
       <c r="H58" t="n">
-        <v>0.655</v>
+        <v>0.658</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3685,26 +3685,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3712,10 +3712,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>12.02</v>
+        <v>3.86</v>
       </c>
       <c r="H59" t="n">
-        <v>0.653</v>
+        <v>0.657</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3756,11 +3756,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>19.5</v>
+        <v>4.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3768,14 +3768,14 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>22.13</v>
+        <v>3.85</v>
       </c>
       <c r="H60" t="n">
-        <v>0.652</v>
+        <v>0.656</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -3797,26 +3797,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3824,14 +3824,14 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5.54</v>
+        <v>3.07</v>
       </c>
       <c r="H61" t="n">
-        <v>0.649</v>
+        <v>0.656</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3853,26 +3853,26 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Al Horford</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>16.5</v>
+        <v>21.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>13.92</v>
+        <v>18.31</v>
       </c>
       <c r="H62" t="n">
-        <v>0.646</v>
+        <v>0.647</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3909,26 +3909,26 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3936,14 +3936,14 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>6.62</v>
+        <v>21.99</v>
       </c>
       <c r="H63" t="n">
         <v>0.645</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3965,26 +3965,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>21.5</v>
+        <v>14.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>18.42</v>
+        <v>12.18</v>
       </c>
       <c r="H64" t="n">
         <v>0.643</v>
@@ -4021,26 +4021,26 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8.5</v>
+        <v>11.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4048,14 +4048,14 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>7.69</v>
+        <v>13.18</v>
       </c>
       <c r="H65" t="n">
-        <v>0.636</v>
+        <v>0.64</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4077,26 +4077,26 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -4104,14 +4104,14 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>13.13</v>
+        <v>2.34</v>
       </c>
       <c r="H66" t="n">
-        <v>0.636</v>
+        <v>0.637</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4133,26 +4133,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>2.35</v>
+        <v>7.68</v>
       </c>
       <c r="H67" t="n">
-        <v>0.634</v>
+        <v>0.637</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4189,26 +4189,26 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4216,14 +4216,14 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>14.9</v>
+        <v>3.07</v>
       </c>
       <c r="H68" t="n">
-        <v>0.632</v>
+        <v>0.631</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4245,26 +4245,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -4272,10 +4272,10 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>8.67</v>
+        <v>4.34</v>
       </c>
       <c r="H69" t="n">
-        <v>0.629</v>
+        <v>0.63</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4301,26 +4301,26 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>2.18</v>
+        <v>6.79</v>
       </c>
       <c r="H70" t="n">
-        <v>0.628</v>
+        <v>0.626</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4357,17 +4357,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4384,14 +4384,14 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>15.25</v>
+        <v>21.85</v>
       </c>
       <c r="H71" t="n">
-        <v>0.627</v>
+        <v>0.626</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -4413,26 +4413,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>6.68</v>
+        <v>14.26</v>
       </c>
       <c r="H72" t="n">
-        <v>0.626</v>
+        <v>0.624</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4484,11 +4484,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>22.69</v>
+        <v>18.49</v>
       </c>
       <c r="H73" t="n">
-        <v>0.625</v>
+        <v>0.624</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4525,26 +4525,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3.5</v>
+        <v>17.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4552,14 +4552,14 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>4.31</v>
+        <v>15.32</v>
       </c>
       <c r="H74" t="n">
-        <v>0.624</v>
+        <v>0.623</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -4581,26 +4581,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -4608,10 +4608,10 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>4.03</v>
+        <v>2.29</v>
       </c>
       <c r="H75" t="n">
-        <v>0.623</v>
+        <v>0.613</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4637,17 +4637,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>2.32</v>
+        <v>6.93</v>
       </c>
       <c r="H76" t="n">
-        <v>0.622</v>
+        <v>0.609</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4693,26 +4693,26 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Corey Kispert</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7.5</v>
+        <v>13.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>6.86</v>
+        <v>11.92</v>
       </c>
       <c r="H77" t="n">
-        <v>0.619</v>
+        <v>0.609</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4749,26 +4749,26 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>19.5</v>
+        <v>2.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4776,10 +4776,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>17.36</v>
+        <v>2.26</v>
       </c>
       <c r="H78" t="n">
-        <v>0.617</v>
+        <v>0.606</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4805,26 +4805,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Luka Doncic</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4832,10 +4832,10 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>6.91</v>
+        <v>4.52</v>
       </c>
       <c r="H79" t="n">
-        <v>0.616</v>
+        <v>0.605</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>18.39</v>
+        <v>18.25</v>
       </c>
       <c r="H80" t="n">
-        <v>0.611</v>
+        <v>0.605</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4917,26 +4917,26 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4944,10 +4944,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>6.92</v>
+        <v>1.36</v>
       </c>
       <c r="H81" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4992,7 +4992,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -5000,14 +5000,14 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>2.25</v>
+        <v>4.38</v>
       </c>
       <c r="H82" t="n">
-        <v>0.609</v>
+        <v>0.599</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5029,26 +5029,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1.35</v>
+        <v>7</v>
       </c>
       <c r="H83" t="n">
-        <v>0.609</v>
+        <v>0.599</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -5085,26 +5085,26 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -5112,14 +5112,14 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>4.5</v>
+        <v>13.9</v>
       </c>
       <c r="H84" t="n">
-        <v>0.607</v>
+        <v>0.59</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5141,26 +5141,26 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>12.5</v>
+        <v>3.5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -5168,14 +5168,14 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>13.07</v>
+        <v>3.59</v>
       </c>
       <c r="H85" t="n">
-        <v>0.596</v>
+        <v>0.583</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5197,26 +5197,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5224,14 +5224,14 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>4.33</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H86" t="n">
-        <v>0.591</v>
+        <v>0.58</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5253,26 +5253,26 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5280,19 +5280,19 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>13.86</v>
+        <v>4.05</v>
       </c>
       <c r="H87" t="n">
-        <v>0.588</v>
+        <v>0.618</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -5309,17 +5309,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5328,7 +5328,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5336,19 +5336,19 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>9.82</v>
+        <v>14.58</v>
       </c>
       <c r="H88" t="n">
-        <v>0.587</v>
+        <v>0.616</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -5365,26 +5365,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>8.5</v>
+        <v>2.5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5392,10 +5392,10 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>8.07</v>
+        <v>2.23</v>
       </c>
       <c r="H89" t="n">
-        <v>0.587</v>
+        <v>0.615</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -5421,17 +5421,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Derrick Jones Jr.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5440,7 +5440,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>3.6</v>
+        <v>4.09</v>
       </c>
       <c r="H90" t="n">
-        <v>0.582</v>
+        <v>0.612</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -5477,26 +5477,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5504,14 +5504,14 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>3.12</v>
+        <v>8.51</v>
       </c>
       <c r="H91" t="n">
-        <v>0.619</v>
+        <v>0.612</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5548,11 +5548,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>20.5</v>
+        <v>4.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5560,14 +5560,14 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>23.08</v>
+        <v>4.11</v>
       </c>
       <c r="H92" t="n">
-        <v>0.614</v>
+        <v>0.607</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5589,17 +5589,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Derrick Jones Jr.</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1.45</v>
+        <v>2.39</v>
       </c>
       <c r="H93" t="n">
-        <v>0.611</v>
+        <v>0.607</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5645,26 +5645,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5672,14 +5672,14 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>9.59</v>
+        <v>3.2</v>
       </c>
       <c r="H94" t="n">
-        <v>0.61</v>
+        <v>0.607</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -5701,26 +5701,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2.5</v>
+        <v>20.5</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5728,14 +5728,14 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>3.21</v>
+        <v>18.98</v>
       </c>
       <c r="H95" t="n">
-        <v>0.61</v>
+        <v>0.601</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5757,26 +5757,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5.5</v>
+        <v>29.5</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5784,14 +5784,14 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>5.07</v>
+        <v>32.17</v>
       </c>
       <c r="H96" t="n">
-        <v>0.606</v>
+        <v>0.6</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5813,26 +5813,26 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5840,10 +5840,10 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>4.15</v>
+        <v>9.69</v>
       </c>
       <c r="H97" t="n">
-        <v>0.599</v>
+        <v>0.598</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5869,26 +5869,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5896,10 +5896,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>12.77</v>
+        <v>14.32</v>
       </c>
       <c r="H98" t="n">
-        <v>0.594</v>
+        <v>0.595</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5925,26 +5925,26 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5952,14 +5952,14 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>14.21</v>
+        <v>5.17</v>
       </c>
       <c r="H99" t="n">
         <v>0.589</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5981,17 +5981,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>5.23</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>0.586</v>
+        <v>0.588</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6037,26 +6037,26 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
           <t>OKC</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -6064,14 +6064,14 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>8.07</v>
+        <v>12.97</v>
       </c>
       <c r="H101" t="n">
-        <v>0.585</v>
+        <v>0.58</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>10.89</v>
+        <v>10.91</v>
       </c>
       <c r="H102" t="n">
-        <v>0.578</v>
+        <v>0.579</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6149,26 +6149,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -6176,14 +6176,14 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>12.99</v>
+        <v>16.66</v>
       </c>
       <c r="H103" t="n">
         <v>0.578</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -6205,26 +6205,26 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="H104" t="n">
-        <v>0.577</v>
+        <v>0.575</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6317,26 +6317,26 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>5.28</v>
+        <v>1.47</v>
       </c>
       <c r="H106" t="n">
-        <v>0.574</v>
+        <v>0.575</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6373,26 +6373,26 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1.47</v>
+        <v>10.08</v>
       </c>
       <c r="H107" t="n">
-        <v>0.572</v>
+        <v>0.574</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6429,26 +6429,26 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>20.86</v>
+        <v>1.92</v>
       </c>
       <c r="H108" t="n">
-        <v>0.571</v>
+        <v>0.573</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6485,26 +6485,26 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6512,10 +6512,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2.4</v>
+        <v>1.51</v>
       </c>
       <c r="H109" t="n">
-        <v>0.571</v>
+        <v>0.572</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6541,26 +6541,26 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.91</v>
+        <v>10.35</v>
       </c>
       <c r="H110" t="n">
-        <v>0.57</v>
+        <v>0.571</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6597,26 +6597,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6624,14 +6624,14 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>13.84</v>
+        <v>13.1</v>
       </c>
       <c r="H111" t="n">
         <v>0.569</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -6653,26 +6653,26 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>15.5</v>
+        <v>5.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6680,14 +6680,14 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>16.49</v>
+        <v>5.31</v>
       </c>
       <c r="H112" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H113" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -6765,26 +6765,26 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>BKN</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3.5</v>
+        <v>25.5</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6792,14 +6792,14 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>3.53</v>
+        <v>27.08</v>
       </c>
       <c r="H114" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -6821,17 +6821,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6848,10 +6848,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>10.25</v>
+        <v>10.36</v>
       </c>
       <c r="H115" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6877,26 +6877,26 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>28.5</v>
+        <v>1.5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>30.37</v>
+        <v>1.88</v>
       </c>
       <c r="H116" t="n">
         <v>0.5620000000000001</v>
@@ -6933,26 +6933,26 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>13.5</v>
+        <v>6.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6960,14 +6960,14 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>12.24</v>
+        <v>7.06</v>
       </c>
       <c r="H117" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -7019,7 +7019,7 @@
         <v>2.92</v>
       </c>
       <c r="H118" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7045,26 +7045,26 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -7072,10 +7072,10 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>7.05</v>
+        <v>13.63</v>
       </c>
       <c r="H119" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7101,17 +7101,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>9.5</v>
+        <v>11.5</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -7128,10 +7128,10 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>10.26</v>
+        <v>12.28</v>
       </c>
       <c r="H120" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7157,26 +7157,26 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Kristaps Porzingis</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -7184,14 +7184,14 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>13.6</v>
+        <v>12.27</v>
       </c>
       <c r="H121" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -7213,17 +7213,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>12.5</v>
+        <v>28.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>13.21</v>
+        <v>30.24</v>
       </c>
       <c r="H122" t="n">
         <v>0.5570000000000001</v>
@@ -7269,17 +7269,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7288,7 +7288,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.63</v>
+        <v>3.56</v>
       </c>
       <c r="H123" t="n">
         <v>0.556</v>
@@ -7355,7 +7355,7 @@
         <v>3.41</v>
       </c>
       <c r="H124" t="n">
-        <v>0.555</v>
+        <v>0.556</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7381,26 +7381,26 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Moses Moody</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1.5</v>
+        <v>21.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1.86</v>
+        <v>22.55</v>
       </c>
       <c r="H125" t="n">
-        <v>0.554</v>
+        <v>0.556</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -7437,26 +7437,26 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>14.5</v>
+        <v>1.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -7464,14 +7464,14 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>15.95</v>
+        <v>1.64</v>
       </c>
       <c r="H126" t="n">
-        <v>0.552</v>
+        <v>0.555</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7493,7 +7493,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -7508,11 +7508,11 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -7520,10 +7520,10 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1.85</v>
+        <v>7.92</v>
       </c>
       <c r="H127" t="n">
-        <v>0.55</v>
+        <v>0.553</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -7549,26 +7549,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Moses Moody</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>8.710000000000001</v>
+        <v>1.85</v>
       </c>
       <c r="H128" t="n">
-        <v>0.55</v>
+        <v>0.551</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7605,26 +7605,26 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>3.5</v>
+        <v>18.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3.91</v>
+        <v>19.49</v>
       </c>
       <c r="H129" t="n">
         <v>0.549</v>
@@ -7661,26 +7661,26 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>7.87</v>
+        <v>9.33</v>
       </c>
       <c r="H130" t="n">
-        <v>0.547</v>
+        <v>0.548</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -7717,26 +7717,26 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>18.5</v>
+        <v>6.5</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>19.5</v>
+        <v>6.97</v>
       </c>
       <c r="H131" t="n">
-        <v>0.547</v>
+        <v>0.546</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7773,26 +7773,26 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1.83</v>
+        <v>3.9</v>
       </c>
       <c r="H132" t="n">
         <v>0.546</v>
@@ -7829,26 +7829,26 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
           <t>LAC</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>ORL</t>
-        </is>
-      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>18.96</v>
+        <v>1.83</v>
       </c>
       <c r="H133" t="n">
         <v>0.545</v>
@@ -7885,26 +7885,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Jonas Valanciunas</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -7912,14 +7912,14 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>5.42</v>
+        <v>7.93</v>
       </c>
       <c r="H134" t="n">
-        <v>0.545</v>
+        <v>0.544</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7971,7 +7971,7 @@
         <v>1.82</v>
       </c>
       <c r="H135" t="n">
-        <v>0.544</v>
+        <v>0.543</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -7997,26 +7997,26 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -8024,10 +8024,10 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>9.92</v>
+        <v>8.5</v>
       </c>
       <c r="H136" t="n">
-        <v>0.543</v>
+        <v>0.541</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -8053,26 +8053,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -8080,10 +8080,10 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>12.08</v>
+        <v>2.83</v>
       </c>
       <c r="H137" t="n">
-        <v>0.54</v>
+        <v>0.538</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>C Tier</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -8109,17 +8109,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Tre Johnson</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>32.5</v>
+        <v>17.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -8136,14 +8136,14 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>31.81</v>
+        <v>18.22</v>
       </c>
       <c r="H138" t="n">
-        <v>0.539</v>
+        <v>0.538</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -8165,26 +8165,26 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -8192,14 +8192,14 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>2.83</v>
+        <v>5.46</v>
       </c>
       <c r="H139" t="n">
-        <v>0.538</v>
+        <v>0.537</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -8221,26 +8221,26 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Jonas Valanciunas</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -8248,10 +8248,10 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>7.86</v>
+        <v>9.85</v>
       </c>
       <c r="H140" t="n">
-        <v>0.537</v>
+        <v>0.536</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -8277,26 +8277,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -8304,14 +8304,14 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>17.8</v>
+        <v>14.24</v>
       </c>
       <c r="H141" t="n">
-        <v>0.534</v>
+        <v>0.536</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -8333,17 +8333,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Luka Doncic</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8352,7 +8352,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>7.5</v>
+        <v>29.5</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -8360,10 +8360,10 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>7.95</v>
+        <v>30.65</v>
       </c>
       <c r="H142" t="n">
-        <v>0.533</v>
+        <v>0.535</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8389,26 +8389,26 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5.5</v>
+        <v>18.5</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -8416,14 +8416,14 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>5.86</v>
+        <v>17.79</v>
       </c>
       <c r="H143" t="n">
-        <v>0.532</v>
+        <v>0.535</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8445,17 +8445,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -8472,14 +8472,14 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>3.53</v>
+        <v>5.86</v>
       </c>
       <c r="H144" t="n">
         <v>0.531</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -8501,26 +8501,26 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>22.5</v>
+        <v>3.5</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -8528,14 +8528,14 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>23.35</v>
+        <v>3.53</v>
       </c>
       <c r="H145" t="n">
-        <v>0.53</v>
+        <v>0.531</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -8557,26 +8557,26 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Kristaps Porzingis</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -8584,10 +8584,10 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>14.05</v>
+        <v>13.07</v>
       </c>
       <c r="H146" t="n">
-        <v>0.527</v>
+        <v>0.53</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -8628,11 +8628,11 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>2.74</v>
+        <v>7.23</v>
       </c>
       <c r="H147" t="n">
-        <v>0.527</v>
+        <v>0.528</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -8669,26 +8669,26 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Corey Kispert</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -8696,10 +8696,10 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1.77</v>
+        <v>11.78</v>
       </c>
       <c r="H148" t="n">
-        <v>0.526</v>
+        <v>0.525</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -8725,17 +8725,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Luka Doncic</t>
+          <t>Dean Wade</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>29.5</v>
+        <v>5.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -8752,10 +8752,10 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>30.35</v>
+        <v>5.71</v>
       </c>
       <c r="H149" t="n">
-        <v>0.526</v>
+        <v>0.523</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -8781,26 +8781,26 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>OKC</t>
-        </is>
-      </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3.5</v>
+        <v>11.5</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -8808,10 +8808,10 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>3.62</v>
+        <v>11.05</v>
       </c>
       <c r="H150" t="n">
-        <v>0.526</v>
+        <v>0.522</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -8837,17 +8837,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -8864,10 +8864,10 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>9.75</v>
+        <v>7.79</v>
       </c>
       <c r="H151" t="n">
-        <v>0.525</v>
+        <v>0.521</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -8908,11 +8908,11 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -8920,14 +8920,14 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>10.8</v>
+        <v>19.18</v>
       </c>
       <c r="H152" t="n">
-        <v>0.524</v>
+        <v>0.519</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -8949,26 +8949,26 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Corey Kispert</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -8976,10 +8976,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>9.720000000000001</v>
+        <v>1.74</v>
       </c>
       <c r="H153" t="n">
-        <v>0.522</v>
+        <v>0.517</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -9005,26 +9005,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>11.5</v>
+        <v>35.5</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -9032,14 +9032,14 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>11.05</v>
+        <v>35.99</v>
       </c>
       <c r="H154" t="n">
-        <v>0.522</v>
+        <v>0.515</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -9061,17 +9061,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>17.5</v>
+        <v>23.5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>17.87</v>
+        <v>23.77</v>
       </c>
       <c r="H155" t="n">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -9117,17 +9117,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Dean Wade</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>2.69</v>
+        <v>3.67</v>
       </c>
       <c r="H156" t="n">
-        <v>0.52</v>
+        <v>0.514</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -9173,17 +9173,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>2.61</v>
+        <v>2.72</v>
       </c>
       <c r="H157" t="n">
-        <v>0.516</v>
+        <v>0.511</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -9229,17 +9229,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -9256,10 +9256,10 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>11.7</v>
+        <v>12.67</v>
       </c>
       <c r="H158" t="n">
-        <v>0.515</v>
+        <v>0.51</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -9285,26 +9285,26 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Moses Moody</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>19.5</v>
+        <v>29.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -9312,14 +9312,14 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>19.26</v>
+        <v>29.7</v>
       </c>
       <c r="H159" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -9341,26 +9341,26 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -9368,10 +9368,10 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>11.64</v>
+        <v>3.68</v>
       </c>
       <c r="H160" t="n">
-        <v>0.513</v>
+        <v>0.501</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -9389,230 +9389,6 @@
         </is>
       </c>
       <c r="L160" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Deandre Ayton</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>LAL</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>BOS</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="E161" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G161" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="H161" t="n">
-        <v>0.511</v>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Under</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Anthony Edwards</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E162" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G162" t="n">
-        <v>29.78</v>
-      </c>
-      <c r="H162" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Over</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Jamal Murray</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>DEN</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E163" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G163" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="H163" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Over</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Michael Porter Jr.</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="E164" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-02-22</t>
-        </is>
-      </c>
-      <c r="G164" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="H164" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Under</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
         </is>

--- a/output/graded_history/user_scorecards/2026-02-22.xlsx
+++ b/output/graded_history/user_scorecards/2026-02-22.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,6 +27,14 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,11 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -535,14 +545,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -591,11 +599,7 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -647,14 +651,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K4" t="n">
+        <v>7</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -703,14 +705,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -759,14 +759,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -815,14 +813,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -871,14 +867,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -927,14 +921,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -983,14 +975,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -1039,14 +1029,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K11" t="n">
+        <v>29</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1095,14 +1083,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1151,14 +1137,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K13" t="n">
+        <v>41</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1207,14 +1191,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1245,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K15" t="n">
+        <v>25</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -1319,14 +1299,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1375,14 +1353,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -1431,14 +1407,12 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1487,14 +1461,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1543,14 +1515,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K20" t="n">
+        <v>16</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1599,14 +1569,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K21" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -1655,14 +1623,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K22" t="n">
+        <v>13</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -1711,14 +1677,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K23" t="n">
+        <v>9</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -1767,14 +1731,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K24" t="n">
+        <v>42</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1823,14 +1785,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1879,14 +1839,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -1935,11 +1893,7 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -1991,14 +1945,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K28" t="n">
+        <v>7</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2047,14 +1999,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2103,14 +2053,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2159,14 +2107,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K31" t="n">
+        <v>25</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2215,14 +2161,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2271,14 +2215,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -2327,14 +2269,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K34" t="n">
+        <v>11</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2383,14 +2323,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K35" t="n">
+        <v>15</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2439,11 +2377,7 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -2495,11 +2429,7 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -2551,14 +2481,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K38" t="n">
+        <v>7</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -2607,14 +2535,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K39" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2663,14 +2589,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K40" t="n">
+        <v>28</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2719,14 +2643,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K41" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2775,14 +2697,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K42" t="n">
+        <v>5</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2831,14 +2751,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K43" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2887,14 +2805,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -2943,14 +2859,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K45" t="n">
+        <v>13</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -2999,14 +2913,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K46" t="n">
+        <v>26</v>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -3055,14 +2967,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K47" t="n">
+        <v>7</v>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -3111,14 +3021,12 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -3167,11 +3075,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -3223,14 +3127,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -3279,14 +3181,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K51" t="n">
+        <v>9</v>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3335,11 +3235,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -3391,11 +3287,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -3447,14 +3339,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3503,11 +3393,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -3559,14 +3445,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -3615,14 +3499,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K57" t="n">
+        <v>9</v>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -3671,14 +3553,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K58" t="n">
+        <v>30</v>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3727,14 +3607,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K59" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3783,11 +3661,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -3839,14 +3713,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K61" t="n">
+        <v>9</v>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -3895,14 +3767,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K62" t="n">
+        <v>18</v>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -3951,14 +3821,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K63" t="n">
+        <v>26</v>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4007,14 +3875,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K64" t="n">
+        <v>24</v>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -4063,14 +3929,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K65" t="n">
+        <v>12</v>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4119,14 +3983,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4175,11 +4037,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -4231,14 +4089,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K68" t="n">
+        <v>3</v>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4287,14 +4143,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K69" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4343,14 +4197,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K70" t="n">
+        <v>6</v>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4399,14 +4251,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K71" t="n">
+        <v>14</v>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -4455,11 +4305,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -4511,14 +4357,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K73" t="n">
+        <v>15</v>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -4567,14 +4411,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K74" t="n">
+        <v>12</v>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4623,14 +4465,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K75" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4679,14 +4519,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K76" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4735,14 +4573,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K77" t="n">
+        <v>9</v>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4791,14 +4627,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -4847,14 +4681,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K79" t="n">
+        <v>5</v>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -4903,14 +4735,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K80" t="n">
+        <v>9</v>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -4959,14 +4789,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5015,14 +4843,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K82" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5071,14 +4897,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K83" t="n">
+        <v>14</v>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5127,14 +4951,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K84" t="n">
+        <v>6</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5183,14 +5005,12 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K85" t="n">
+        <v>3</v>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5239,11 +5059,7 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -5295,14 +5111,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K87" t="n">
+        <v>6</v>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5351,14 +5165,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K88" t="n">
+        <v>22</v>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5407,14 +5219,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5463,11 +5273,7 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -5519,14 +5325,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K91" t="n">
+        <v>10</v>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5575,14 +5379,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K92" t="n">
+        <v>7</v>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5631,14 +5433,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K93" t="n">
+        <v>2</v>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5687,14 +5487,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K94" t="n">
+        <v>4</v>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5743,14 +5541,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K95" t="n">
+        <v>29</v>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5799,14 +5595,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K96" t="n">
+        <v>24</v>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5855,14 +5649,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K97" t="n">
+        <v>4</v>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5911,14 +5703,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K98" t="n">
+        <v>7</v>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5967,14 +5757,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K99" t="n">
+        <v>5</v>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6023,14 +5811,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K100" t="n">
+        <v>7</v>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6079,14 +5865,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K101" t="n">
+        <v>14</v>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6135,14 +5919,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K102" t="n">
+        <v>4</v>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6191,14 +5973,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K103" t="n">
+        <v>15</v>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6247,14 +6027,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K104" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6303,14 +6081,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K105" t="n">
+        <v>6</v>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6359,14 +6135,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K106" t="n">
+        <v>2</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6415,14 +6189,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K107" t="n">
+        <v>12</v>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6471,11 +6243,7 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -6527,14 +6295,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K109" t="n">
+        <v>2</v>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6583,14 +6349,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K110" t="n">
+        <v>8</v>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6639,14 +6403,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K111" t="n">
+        <v>20</v>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6695,14 +6457,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K112" t="n">
+        <v>4</v>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6751,14 +6511,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K113" t="n">
+        <v>2</v>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6807,14 +6565,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K114" t="n">
+        <v>28</v>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -6863,14 +6619,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K115" t="n">
+        <v>7</v>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6919,14 +6673,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -6975,14 +6727,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K117" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7031,14 +6781,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K118" t="n">
+        <v>4</v>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7087,14 +6835,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K119" t="n">
+        <v>3</v>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7143,11 +6889,7 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -7199,14 +6941,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K121" t="n">
+        <v>8</v>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7255,11 +6995,7 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -7311,14 +7047,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K123" t="n">
+        <v>5</v>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7367,14 +7101,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K124" t="n">
+        <v>2</v>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7423,14 +7155,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K125" t="n">
+        <v>18</v>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7479,14 +7209,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K126" t="n">
+        <v>3</v>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7535,14 +7263,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K127" t="n">
+        <v>5</v>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7591,14 +7317,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K128" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7647,14 +7371,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K129" t="n">
+        <v>25</v>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7703,14 +7425,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K130" t="n">
+        <v>9</v>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7759,11 +7479,7 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -7815,14 +7531,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K132" t="n">
+        <v>3</v>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7871,14 +7585,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K133" t="n">
+        <v>1</v>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7927,14 +7639,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K134" t="n">
+        <v>6</v>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -7983,14 +7693,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8039,14 +7747,12 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K136" t="n">
+        <v>20</v>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -8095,11 +7801,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -8151,14 +7853,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K138" t="n">
+        <v>15</v>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8207,14 +7907,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K139" t="n">
+        <v>7</v>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8263,14 +7961,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K140" t="n">
+        <v>5</v>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8319,14 +8015,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K141" t="n">
+        <v>22</v>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -8375,14 +8069,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K142" t="n">
+        <v>25</v>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8431,14 +8123,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K143" t="n">
+        <v>21</v>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8487,14 +8177,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K144" t="n">
+        <v>5</v>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8543,14 +8231,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K145" t="n">
+        <v>2</v>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -8599,11 +8285,7 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr">
         <is>
           <t>Pending / Not Found</t>
@@ -8655,14 +8337,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K147" t="n">
+        <v>7</v>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -8711,14 +8391,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K148" t="n">
+        <v>17</v>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -8767,14 +8445,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8823,14 +8499,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K150" t="n">
+        <v>20</v>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8879,14 +8553,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K151" t="n">
+        <v>8</v>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -8935,14 +8607,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K152" t="n">
+        <v>20</v>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -8991,14 +8661,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -9047,14 +8715,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K154" t="n">
+        <v>25</v>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -9103,14 +8769,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K155" t="n">
+        <v>24</v>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -9159,14 +8823,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K156" t="n">
+        <v>3</v>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -9215,14 +8877,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -9271,14 +8931,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K158" t="n">
+        <v>9</v>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -9327,14 +8985,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K159" t="n">
+        <v>28</v>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -9383,14 +9039,12 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K160" t="n">
+        <v>4</v>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>

--- a/output/graded_history/user_scorecards/2026-02-22.xlsx
+++ b/output/graded_history/user_scorecards/2026-02-22.xlsx
@@ -30,11 +30,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="2">
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jonas Valanciunas</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.62</v>
+        <v>6.48</v>
       </c>
       <c r="H2" t="n">
-        <v>0.854</v>
+        <v>0.676</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>RJ Barrett</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -584,14 +584,14 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>31.3</v>
+        <v>23.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.777</v>
+        <v>0.673</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -599,36 +599,38 @@
           <t>S Tier</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K3" t="n">
+        <v>16</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jaylen Brown</t>
+          <t>Naji Marshall</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -636,10 +638,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3.34</v>
+        <v>8.56</v>
       </c>
       <c r="H4" t="n">
-        <v>0.756</v>
+        <v>0.667</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -652,37 +654,37 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -690,14 +692,14 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.99</v>
+        <v>11.62</v>
       </c>
       <c r="H5" t="n">
-        <v>0.746</v>
+        <v>0.662</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -706,9 +708,9 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -717,17 +719,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brandon Ingram</t>
+          <t>Jonas Valanciunas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -736,7 +738,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -744,10 +746,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.53</v>
+        <v>0.61</v>
       </c>
       <c r="H6" t="n">
-        <v>0.737</v>
+        <v>0.857</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -756,13 +758,13 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -771,26 +773,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jalen Johnson</t>
+          <t>Tyus Jones</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -798,10 +800,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5.57</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
-        <v>0.731</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -810,13 +812,13 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -825,26 +827,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -852,10 +854,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="H8" t="n">
-        <v>0.729</v>
+        <v>0.775</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -864,41 +866,41 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tyrese Maxey</t>
+          <t>Joan Beringer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>PHI</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -906,10 +908,10 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5.02</v>
+        <v>4.19</v>
       </c>
       <c r="H9" t="n">
-        <v>0.716</v>
+        <v>0.754</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -918,41 +920,41 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chet Holmgren</t>
+          <t>Draymond Green</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8.5</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -960,10 +962,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6.64</v>
+        <v>3.24</v>
       </c>
       <c r="H10" t="n">
-        <v>0.713</v>
+        <v>0.752</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -972,41 +974,39 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>S Tier</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+          <t>A Tier</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brandon Miller</t>
+          <t>Jaylen Brown</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>33.5</v>
+        <v>4.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1014,10 +1014,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>29.23</v>
+        <v>3.15</v>
       </c>
       <c r="H11" t="n">
-        <v>0.712</v>
+        <v>0.748</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1026,41 +1026,41 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Tyrese Maxey</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1068,53 +1068,53 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12.76</v>
+        <v>4.74</v>
       </c>
       <c r="H12" t="n">
-        <v>0.705</v>
+        <v>0.74</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25.5</v>
+        <v>3.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1122,25 +1122,25 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>29.56</v>
+        <v>2.53</v>
       </c>
       <c r="H13" t="n">
-        <v>0.704</v>
+        <v>0.738</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>41</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -1149,17 +1149,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jock Landale</t>
+          <t>Kristaps Porzingis</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1176,10 +1176,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="H14" t="n">
-        <v>0.701</v>
+        <v>0.737</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1188,41 +1188,39 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>S Tier</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
+          <t>A Tier</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dyson Daniels</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>23.5</v>
+        <v>2.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1230,10 +1228,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>19.53</v>
+        <v>1.79</v>
       </c>
       <c r="H15" t="n">
-        <v>0.699</v>
+        <v>0.734</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1242,32 +1240,32 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LaMelo Ball</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1276,7 +1274,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1284,10 +1282,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>6.35</v>
+        <v>1.3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.695</v>
+        <v>0.726</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1296,13 +1294,13 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -1311,26 +1309,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Donovan Mitchell</t>
+          <t>Jalen Johnson</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1338,10 +1336,10 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.83</v>
+        <v>5.68</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.723</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1350,32 +1348,32 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Brandon Ingram</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1392,10 +1390,10 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1404,22 +1402,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>S Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Joan Beringer</t>
+          <t>Ayo Dosunmu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1438,7 +1436,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1446,10 +1444,10 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.95</v>
+        <v>2.74</v>
       </c>
       <c r="H19" t="n">
-        <v>0.921</v>
+        <v>0.718</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1462,37 +1460,37 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RJ Barrett</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1500,10 +1498,10 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>23.23</v>
+        <v>1.89</v>
       </c>
       <c r="H20" t="n">
-        <v>0.769</v>
+        <v>0.713</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1516,37 +1514,37 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ayo Dosunmu</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1554,10 +1552,10 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.34</v>
+        <v>1.1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.758</v>
+        <v>0.712</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1570,37 +1568,37 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kyshawn George</t>
+          <t>Kawhi Leonard</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1608,10 +1606,10 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8.75</v>
+        <v>3.53</v>
       </c>
       <c r="H22" t="n">
-        <v>0.743</v>
+        <v>0.71</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1623,38 +1621,36 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>13</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ryan Kalkbrenner</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1662,10 +1658,10 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>6.02</v>
+        <v>1.18</v>
       </c>
       <c r="H23" t="n">
-        <v>0.741</v>
+        <v>0.704</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1678,37 +1674,37 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Payton Pritchard</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>27.5</v>
+        <v>2.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1716,14 +1712,14 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>33.61</v>
+        <v>1.93</v>
       </c>
       <c r="H24" t="n">
-        <v>0.724</v>
+        <v>0.696</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1732,9 +1728,9 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>42</v>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -1743,26 +1739,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>CJ McCollum</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1770,10 +1766,10 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.84</v>
+        <v>2.81</v>
       </c>
       <c r="H25" t="n">
-        <v>0.72</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1786,37 +1782,37 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tyus Jones</t>
+          <t>Ryan Kalkbrenner</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1824,10 +1820,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5.48</v>
+        <v>6.18</v>
       </c>
       <c r="H26" t="n">
-        <v>0.718</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1840,28 +1836,28 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Dyson Daniels</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1870,7 +1866,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1878,10 +1874,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3.49</v>
+        <v>4.54</v>
       </c>
       <c r="H27" t="n">
-        <v>0.716</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1893,36 +1889,38 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K27" t="n">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1930,10 +1928,10 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>11.29</v>
+        <v>6.58</v>
       </c>
       <c r="H28" t="n">
-        <v>0.713</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1945,29 +1943,27 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>7</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jared McCain</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1984,10 +1980,10 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="H29" t="n">
-        <v>0.711</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2000,9 +1996,9 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2011,26 +2007,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Klay Thompson</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2038,10 +2034,10 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.32</v>
+        <v>2.02</v>
       </c>
       <c r="H30" t="n">
-        <v>0.711</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2054,37 +2050,37 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>27.5</v>
+        <v>4.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2092,10 +2088,10 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>24.09</v>
+        <v>3.86</v>
       </c>
       <c r="H31" t="n">
-        <v>0.709</v>
+        <v>0.675</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2108,9 +2104,9 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>25</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2119,17 +2115,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Grant Williams</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2146,10 +2142,10 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="H32" t="n">
-        <v>0.698</v>
+        <v>0.667</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2162,28 +2158,28 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Egor Demin</t>
+          <t>Kyle Kuzma</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2192,7 +2188,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2200,10 +2196,10 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.92</v>
+        <v>2.35</v>
       </c>
       <c r="H33" t="n">
-        <v>0.665</v>
+        <v>0.662</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2216,37 +2212,37 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bub Carrington</t>
+          <t>Jalen Suggs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>17.5</v>
+        <v>3.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2254,10 +2250,10 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>15.96</v>
+        <v>3.29</v>
       </c>
       <c r="H34" t="n">
-        <v>0.661</v>
+        <v>0.662</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2269,38 +2265,36 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K34" t="n">
-        <v>11</v>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>10.5</v>
+        <v>7.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2308,14 +2302,14 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>12.2</v>
+        <v>6.53</v>
       </c>
       <c r="H35" t="n">
-        <v>0.66</v>
+        <v>0.661</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2324,9 +2318,9 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2335,26 +2329,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4.5</v>
+        <v>26.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2362,14 +2356,14 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3.86</v>
+        <v>30.11</v>
       </c>
       <c r="H36" t="n">
-        <v>0.654</v>
+        <v>0.644</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2387,26 +2381,26 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bennedict Mathurin</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2414,10 +2408,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>3.35</v>
+        <v>13.57</v>
       </c>
       <c r="H37" t="n">
-        <v>0.65</v>
+        <v>0.641</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2429,27 +2423,29 @@
           <t>A Tier</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K37" t="n">
+        <v>17</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Anthony Black</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2458,7 +2454,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2466,10 +2462,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2.99</v>
+        <v>3.97</v>
       </c>
       <c r="H38" t="n">
-        <v>0.649</v>
+        <v>0.635</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2482,37 +2478,37 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Anthony Black</t>
+          <t>Egor Demin</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>15.5</v>
+        <v>3.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2520,10 +2516,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>13.15</v>
+        <v>3.09</v>
       </c>
       <c r="H39" t="n">
-        <v>0.648</v>
+        <v>0.627</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2536,37 +2532,37 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20.5</v>
+        <v>27.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2574,14 +2570,14 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>23.18</v>
+        <v>24.2</v>
       </c>
       <c r="H40" t="n">
-        <v>0.648</v>
+        <v>0.627</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2590,9 +2586,9 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>28</v>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
+        <v>25</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2601,26 +2597,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LeBron James</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2628,14 +2624,14 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4.85</v>
+        <v>12.48</v>
       </c>
       <c r="H41" t="n">
-        <v>0.64</v>
+        <v>0.626</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2644,9 +2640,9 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2655,26 +2651,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Nolan Traore</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2682,14 +2678,14 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>6.02</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.64</v>
+        <v>0.624</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2698,37 +2694,37 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>LaMelo Ball</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3.5</v>
+        <v>20.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2736,14 +2732,14 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>3.13</v>
+        <v>22.42</v>
       </c>
       <c r="H43" t="n">
-        <v>0.637</v>
+        <v>0.621</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -2752,9 +2748,9 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
+        <v>37</v>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2763,26 +2759,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Luka Doncic</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7.5</v>
+        <v>19.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2790,14 +2786,14 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>6.76</v>
+        <v>21.32</v>
       </c>
       <c r="H44" t="n">
-        <v>0.631</v>
+        <v>0.617</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -2806,9 +2802,9 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
+        <v>20</v>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2817,17 +2813,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Immanuel Quickley</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2836,7 +2832,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2844,10 +2840,10 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>16.52</v>
+        <v>20.01</v>
       </c>
       <c r="H45" t="n">
-        <v>0.629</v>
+        <v>0.615</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2860,18 +2856,18 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Dean Wade</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2890,7 +2886,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>25.5</v>
+        <v>10.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2898,14 +2894,14 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>30.01</v>
+        <v>8.84</v>
       </c>
       <c r="H46" t="n">
-        <v>0.626</v>
+        <v>0.615</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2914,9 +2910,9 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>26</v>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2925,26 +2921,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2952,10 +2948,10 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>7.6</v>
+        <v>6.89</v>
       </c>
       <c r="H47" t="n">
-        <v>0.624</v>
+        <v>0.614</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2968,9 +2964,9 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>7</v>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -2979,26 +2975,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3006,10 +3002,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.41</v>
+        <v>8.26</v>
       </c>
       <c r="H48" t="n">
-        <v>0.623</v>
+        <v>0.609</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3022,37 +3018,37 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kristaps Porzingis</t>
+          <t>Desmond Bane</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1.5</v>
+        <v>18.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3060,51 +3056,53 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.31</v>
+        <v>21.54</v>
       </c>
       <c r="H49" t="n">
-        <v>0.68</v>
+        <v>0.608</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>B Tier</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+          <t>A Tier</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>34</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1.5</v>
+        <v>9.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3112,10 +3110,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.32</v>
+        <v>8.43</v>
       </c>
       <c r="H50" t="n">
-        <v>0.678</v>
+        <v>0.605</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3124,13 +3122,13 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -3139,26 +3137,26 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Immanuel Quickley</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6.5</v>
+        <v>17.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3166,10 +3164,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>5.55</v>
+        <v>16.07</v>
       </c>
       <c r="H51" t="n">
-        <v>0.678</v>
+        <v>0.603</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3178,32 +3176,32 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>B Tier</t>
+          <t>A Tier</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Chet Holmgren</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3212,7 +3210,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3220,10 +3218,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>4.59</v>
+        <v>7.53</v>
       </c>
       <c r="H52" t="n">
-        <v>0.677</v>
+        <v>0.658</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3235,36 +3233,38 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K52" t="n">
+        <v>15</v>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3272,14 +3272,14 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>4.67</v>
+        <v>3.38</v>
       </c>
       <c r="H53" t="n">
-        <v>0.674</v>
+        <v>0.657</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3297,26 +3297,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Donovan Mitchell</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3324,10 +3324,10 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2.06</v>
+        <v>2.99</v>
       </c>
       <c r="H54" t="n">
-        <v>0.674</v>
+        <v>0.654</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3340,9 +3340,9 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>5</v>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -3351,26 +3351,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Jalen Suggs</t>
+          <t>Isaiah Joe</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3378,14 +3378,14 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>3.02</v>
+        <v>2.2</v>
       </c>
       <c r="H55" t="n">
-        <v>0.667</v>
+        <v>0.646</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3393,36 +3393,38 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Cason Wallace</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3430,14 +3432,14 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>2.44</v>
+        <v>4.51</v>
       </c>
       <c r="H56" t="n">
-        <v>0.663</v>
+        <v>0.645</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3446,9 +3448,9 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -3457,7 +3459,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ryan Rollins</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3476,7 +3478,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3484,14 +3486,14 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>5.62</v>
+        <v>1.39</v>
       </c>
       <c r="H57" t="n">
-        <v>0.66</v>
+        <v>0.645</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3500,37 +3502,37 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Al Horford</t>
+          <t>Kyshawn George</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>16.5</v>
+        <v>3.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3538,10 +3540,10 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>13.7</v>
+        <v>3.02</v>
       </c>
       <c r="H58" t="n">
-        <v>0.658</v>
+        <v>0.644</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3554,18 +3556,18 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3580,11 +3582,11 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3592,10 +3594,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3.86</v>
+        <v>9.27</v>
       </c>
       <c r="H59" t="n">
-        <v>0.657</v>
+        <v>0.642</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3607,29 +3609,27 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K59" t="n">
-        <v>6</v>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Draymond Green</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3.85</v>
+        <v>3.03</v>
       </c>
       <c r="H60" t="n">
-        <v>0.656</v>
+        <v>0.64</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3661,36 +3661,38 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K60" t="n">
+        <v>7</v>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Brandin Podziemski</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3698,14 +3700,14 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>3.07</v>
+        <v>12.09</v>
       </c>
       <c r="H61" t="n">
-        <v>0.656</v>
+        <v>0.639</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3714,37 +3716,37 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Julius Randle</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21.5</v>
+        <v>9.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3752,10 +3754,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>18.31</v>
+        <v>8.5</v>
       </c>
       <c r="H62" t="n">
-        <v>0.647</v>
+        <v>0.639</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3768,37 +3770,37 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3806,14 +3808,14 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>21.99</v>
+        <v>6.73</v>
       </c>
       <c r="H63" t="n">
-        <v>0.645</v>
+        <v>0.638</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3822,9 +3824,9 @@
         </is>
       </c>
       <c r="K63" t="n">
-        <v>26</v>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -3833,26 +3835,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jamal Shead</t>
+          <t>Luka Doncic</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>14.5</v>
+        <v>7.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3860,10 +3862,10 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>12.18</v>
+        <v>6.72</v>
       </c>
       <c r="H64" t="n">
-        <v>0.643</v>
+        <v>0.636</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3876,37 +3878,37 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3914,14 +3916,14 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>13.18</v>
+        <v>5</v>
       </c>
       <c r="H65" t="n">
-        <v>0.64</v>
+        <v>0.631</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3930,9 +3932,9 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>12</v>
-      </c>
-      <c r="L65" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -3968,10 +3970,10 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="H66" t="n">
-        <v>0.637</v>
+        <v>0.63</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3986,7 +3988,7 @@
       <c r="K66" t="n">
         <v>1</v>
       </c>
-      <c r="L66" s="3" t="inlineStr">
+      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -3995,26 +3997,26 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -4022,10 +4024,10 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>7.68</v>
+        <v>1.49</v>
       </c>
       <c r="H67" t="n">
-        <v>0.637</v>
+        <v>0.629</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4037,27 +4039,29 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Desmond Bane</t>
+          <t>Julius Randle</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4066,7 +4070,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -4074,10 +4078,10 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>3.07</v>
+        <v>4.05</v>
       </c>
       <c r="H68" t="n">
-        <v>0.631</v>
+        <v>0.627</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4092,7 +4096,7 @@
       <c r="K68" t="n">
         <v>3</v>
       </c>
-      <c r="L68" s="3" t="inlineStr">
+      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -4101,22 +4105,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -4128,14 +4132,14 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>4.34</v>
+        <v>3.14</v>
       </c>
       <c r="H69" t="n">
-        <v>0.63</v>
+        <v>0.627</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4144,9 +4148,9 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>4</v>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -4155,17 +4159,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4174,7 +4178,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -4182,10 +4186,10 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>6.79</v>
+        <v>4.94</v>
       </c>
       <c r="H70" t="n">
-        <v>0.626</v>
+        <v>0.627</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4197,38 +4201,36 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K70" t="n">
-        <v>6</v>
-      </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Grant Williams</t>
+          <t>Moses Moody</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>19.5</v>
+        <v>1.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -4236,10 +4238,10 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>21.85</v>
+        <v>2.11</v>
       </c>
       <c r="H71" t="n">
-        <v>0.626</v>
+        <v>0.623</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4252,37 +4254,37 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tristan Vukcevic</t>
+          <t>LeBron James</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -4290,14 +4292,14 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>14.26</v>
+        <v>6.03</v>
       </c>
       <c r="H72" t="n">
-        <v>0.624</v>
+        <v>0.62</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4305,36 +4307,38 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K72" t="n">
+        <v>5</v>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cam Thomas</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -4342,14 +4346,14 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>18.49</v>
+        <v>4.13</v>
       </c>
       <c r="H73" t="n">
-        <v>0.624</v>
+        <v>0.618</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4357,38 +4361,36 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K73" t="n">
-        <v>15</v>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Klay Thompson</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>17.5</v>
+        <v>3.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -4396,10 +4398,10 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>15.32</v>
+        <v>3.7</v>
       </c>
       <c r="H74" t="n">
-        <v>0.623</v>
+        <v>0.613</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4412,9 +4414,9 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>12</v>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -4423,7 +4425,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Bilal Coulibaly</t>
+          <t>Bub Carrington</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4438,7 +4440,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -4450,14 +4452,14 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>2.29</v>
+        <v>3.21</v>
       </c>
       <c r="H75" t="n">
-        <v>0.613</v>
+        <v>0.612</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -4466,9 +4468,9 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -4477,22 +4479,22 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Neemias Queta</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -4504,14 +4506,14 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>6.93</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H76" t="n">
         <v>0.609</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4520,9 +4522,9 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -4531,26 +4533,26 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Corey Kispert</t>
+          <t>Bilal Coulibaly</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -4558,10 +4560,10 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>11.92</v>
+        <v>3.61</v>
       </c>
       <c r="H77" t="n">
-        <v>0.609</v>
+        <v>0.607</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4574,9 +4576,9 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>9</v>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -4585,17 +4587,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Onyeka Okongwu</t>
+          <t>Sam Hauser</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4604,7 +4606,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -4612,10 +4614,10 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>2.26</v>
+        <v>1.51</v>
       </c>
       <c r="H78" t="n">
-        <v>0.606</v>
+        <v>0.6</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4628,37 +4630,37 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4.5</v>
+        <v>18.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4666,14 +4668,14 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>4.52</v>
+        <v>20.56</v>
       </c>
       <c r="H79" t="n">
-        <v>0.605</v>
+        <v>0.593</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4682,28 +4684,28 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tim Hardaway Jr.</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4712,7 +4714,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4720,14 +4722,14 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>18.25</v>
+        <v>16.98</v>
       </c>
       <c r="H80" t="n">
-        <v>0.605</v>
+        <v>0.584</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4736,37 +4738,37 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Paolo Banchero</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -4774,10 +4776,10 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1.36</v>
+        <v>7.28</v>
       </c>
       <c r="H81" t="n">
-        <v>0.605</v>
+        <v>0.578</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4790,28 +4792,28 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Derrick White</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4820,7 +4822,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -4828,10 +4830,10 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>4.38</v>
+        <v>7.19</v>
       </c>
       <c r="H82" t="n">
-        <v>0.599</v>
+        <v>0.577</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4844,9 +4846,9 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>6</v>
-      </c>
-      <c r="L82" s="3" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -4855,17 +4857,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Paolo Banchero</t>
+          <t>Joel Embiid</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4874,7 +4876,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -4882,10 +4884,10 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="H83" t="n">
-        <v>0.599</v>
+        <v>0.569</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4897,38 +4899,36 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K83" t="n">
-        <v>14</v>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -4936,14 +4936,14 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>13.9</v>
+        <v>4.31</v>
       </c>
       <c r="H84" t="n">
-        <v>0.59</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4954,7 +4954,7 @@
       <c r="K84" t="n">
         <v>6</v>
       </c>
-      <c r="L84" s="2" t="inlineStr">
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -4963,17 +4963,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Nickeil Alexander-Walker</t>
+          <t>Isaiah Hartenstein</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>3.59</v>
+        <v>8.4</v>
       </c>
       <c r="H85" t="n">
-        <v>0.583</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -5006,9 +5006,9 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>3</v>
-      </c>
-      <c r="L85" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -5017,26 +5017,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Joel Embiid</t>
+          <t>De'Anthony Melton</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -5044,14 +5044,14 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>8.130000000000001</v>
+        <v>15.64</v>
       </c>
       <c r="H86" t="n">
-        <v>0.58</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -5059,36 +5059,38 @@
           <t>B Tier</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K86" t="n">
+        <v>20</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Donte DiVincenzo</t>
+          <t>James Harden</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -5096,10 +5098,10 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>4.05</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H87" t="n">
-        <v>0.618</v>
+        <v>0.554</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5108,13 +5110,13 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>C Tier</t>
+          <t>B Tier</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>6</v>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -5123,17 +5125,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Kon Knueppel</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5142,7 +5144,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>12.5</v>
+        <v>20.5</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -5150,10 +5152,10 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>14.58</v>
+        <v>22.14</v>
       </c>
       <c r="H88" t="n">
-        <v>0.616</v>
+        <v>0.552</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5162,13 +5164,13 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>C Tier</t>
+          <t>B Tier</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>22</v>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -5177,26 +5179,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Julian Strawther</t>
+          <t>VJ Edgecombe</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2.5</v>
+        <v>15.5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -5204,27 +5206,27 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>2.23</v>
+        <v>16.89</v>
       </c>
       <c r="H89" t="n">
-        <v>0.615</v>
+        <v>0.551</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>C Tier</t>
+          <t>B Tier</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L89" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
@@ -5246,11 +5248,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -5258,10 +5260,10 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>4.09</v>
+        <v>1.49</v>
       </c>
       <c r="H90" t="n">
-        <v>0.612</v>
+        <v>0.596</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5283,26 +5285,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Neemias Queta</t>
+          <t>Jamal Shead</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -5310,10 +5312,10 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>8.51</v>
+        <v>2.19</v>
       </c>
       <c r="H91" t="n">
-        <v>0.612</v>
+        <v>0.595</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5326,9 +5328,9 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>10</v>
-      </c>
-      <c r="L91" s="3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -5337,26 +5339,26 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4.5</v>
+        <v>8.5</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -5364,14 +5366,14 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>4.11</v>
+        <v>10.07</v>
       </c>
       <c r="H92" t="n">
-        <v>0.607</v>
+        <v>0.592</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5380,37 +5382,37 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>De'Anthony Melton</t>
+          <t>Christian Braun</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2.5</v>
+        <v>11.5</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -5418,14 +5420,14 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>2.39</v>
+        <v>13.58</v>
       </c>
       <c r="H93" t="n">
-        <v>0.607</v>
+        <v>0.592</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5434,9 +5436,9 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>2</v>
-      </c>
-      <c r="L93" s="3" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -5445,17 +5447,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -5464,7 +5466,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -5472,10 +5474,10 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>3.2</v>
+        <v>1.99</v>
       </c>
       <c r="H94" t="n">
-        <v>0.607</v>
+        <v>0.59</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5488,28 +5490,28 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Evan Mobley</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -5518,7 +5520,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -5526,14 +5528,14 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>18.98</v>
+        <v>24.53</v>
       </c>
       <c r="H95" t="n">
-        <v>0.601</v>
+        <v>0.59</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5542,9 +5544,9 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>29</v>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -5553,26 +5555,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Austin Reaves</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>29.5</v>
+        <v>10.5</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -5580,10 +5582,10 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>32.17</v>
+        <v>12.79</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5596,37 +5598,37 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Naji Marshall</t>
+          <t>Pat Spencer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>10.5</v>
+        <v>3.5</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -5634,14 +5636,14 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>9.69</v>
+        <v>4.26</v>
       </c>
       <c r="H97" t="n">
-        <v>0.598</v>
+        <v>0.588</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5650,37 +5652,37 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L97" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Rui Hachimura</t>
+          <t>Myles Turner</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -5688,10 +5690,10 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>14.32</v>
+        <v>14.03</v>
       </c>
       <c r="H98" t="n">
-        <v>0.595</v>
+        <v>0.586</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5704,11 +5706,11 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -5730,11 +5732,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5.5</v>
+        <v>20.5</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -5742,10 +5744,10 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>5.17</v>
+        <v>16.74</v>
       </c>
       <c r="H99" t="n">
-        <v>0.589</v>
+        <v>0.586</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5758,9 +5760,9 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>5</v>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -5769,26 +5771,26 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Brook Lopez</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>8.5</v>
+        <v>1.5</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -5796,14 +5798,14 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>8.050000000000001</v>
+        <v>1.96</v>
       </c>
       <c r="H100" t="n">
-        <v>0.588</v>
+        <v>0.584</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5811,38 +5813,36 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K100" t="n">
-        <v>7</v>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>12.97</v>
+        <v>3.03</v>
       </c>
       <c r="H101" t="n">
-        <v>0.58</v>
+        <v>0.584</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5866,9 +5866,9 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>14</v>
-      </c>
-      <c r="L101" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -5877,26 +5877,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Deandre Ayton</t>
+          <t>Dominick Barlow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -5904,14 +5904,14 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>10.91</v>
+        <v>5.14</v>
       </c>
       <c r="H102" t="n">
-        <v>0.579</v>
+        <v>0.583</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -5920,9 +5920,9 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>4</v>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -5931,26 +5931,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Baylor Scheierman</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>15.5</v>
+        <v>1.5</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>16.66</v>
+        <v>2.18</v>
       </c>
       <c r="H103" t="n">
-        <v>0.578</v>
+        <v>0.583</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5974,28 +5974,28 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Quentin Grimes</t>
+          <t>Corey Kispert</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -6012,10 +6012,10 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>2.38</v>
+        <v>2.54</v>
       </c>
       <c r="H104" t="n">
-        <v>0.575</v>
+        <v>0.582</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6028,9 +6028,9 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -6039,26 +6039,26 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Michael Porter Jr.</t>
+          <t>Jock Landale</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
           <t>BKN</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6066,10 +6066,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2.99</v>
+        <v>9.59</v>
       </c>
       <c r="H105" t="n">
-        <v>0.575</v>
+        <v>0.581</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6082,9 +6082,9 @@
         </is>
       </c>
       <c r="K105" t="n">
-        <v>6</v>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -6093,26 +6093,26 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Nolan Traore</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6120,14 +6120,14 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1.47</v>
+        <v>12.35</v>
       </c>
       <c r="H106" t="n">
-        <v>0.575</v>
+        <v>0.581</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -6136,37 +6136,37 @@
         </is>
       </c>
       <c r="K106" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Sam Merrill</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6174,14 +6174,14 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>10.08</v>
+        <v>1.98</v>
       </c>
       <c r="H107" t="n">
-        <v>0.574</v>
+        <v>0.581</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -6190,9 +6190,9 @@
         </is>
       </c>
       <c r="K107" t="n">
-        <v>12</v>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -6201,26 +6201,26 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Brook Lopez</t>
+          <t>Brandin Podziemski</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>1.92</v>
+        <v>5.33</v>
       </c>
       <c r="H108" t="n">
-        <v>0.573</v>
+        <v>0.58</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6243,36 +6243,38 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K108" t="n">
+        <v>15</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Jarrett Allen</t>
+          <t>Deandre Ayton</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -6280,10 +6282,10 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1.51</v>
+        <v>7.35</v>
       </c>
       <c r="H109" t="n">
-        <v>0.572</v>
+        <v>0.58</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6296,37 +6298,37 @@
         </is>
       </c>
       <c r="K109" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Noah Clowney</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -6334,14 +6336,14 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>10.35</v>
+        <v>1.44</v>
       </c>
       <c r="H110" t="n">
-        <v>0.571</v>
+        <v>0.579</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -6350,37 +6352,37 @@
         </is>
       </c>
       <c r="K110" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Nikola Jokic</t>
+          <t>Al Horford</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
           <t>DEN</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>GSW</t>
-        </is>
-      </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>REB</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6388,10 +6390,10 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>13.1</v>
+        <v>5.41</v>
       </c>
       <c r="H111" t="n">
-        <v>0.569</v>
+        <v>0.578</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6404,37 +6406,37 @@
         </is>
       </c>
       <c r="K111" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Collin Murray-Boyles</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5.5</v>
+        <v>1.5</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6442,10 +6444,10 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>5.31</v>
+        <v>1.49</v>
       </c>
       <c r="H112" t="n">
-        <v>0.569</v>
+        <v>0.577</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -6458,28 +6460,28 @@
         </is>
       </c>
       <c r="K112" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L112" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Baylor Scheierman</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -6488,7 +6490,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6496,14 +6498,14 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="H113" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -6514,7 +6516,7 @@
       <c r="K113" t="n">
         <v>2</v>
       </c>
-      <c r="L113" s="3" t="inlineStr">
+      <c r="L113" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -6523,26 +6525,26 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CJ McCollum</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>25.5</v>
+        <v>2.5</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6550,10 +6552,10 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>27.08</v>
+        <v>2.98</v>
       </c>
       <c r="H114" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -6566,9 +6568,9 @@
         </is>
       </c>
       <c r="K114" t="n">
-        <v>28</v>
-      </c>
-      <c r="L114" s="3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -6577,17 +6579,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sam Hauser</t>
+          <t>Jarrett Allen</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -6596,7 +6598,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6604,10 +6606,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>10.36</v>
+        <v>16.17</v>
       </c>
       <c r="H115" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.57</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -6620,9 +6622,9 @@
         </is>
       </c>
       <c r="K115" t="n">
-        <v>7</v>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
+        <v>11</v>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -6631,26 +6633,26 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AJ Green</t>
+          <t>Dennis Schroder</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6658,10 +6660,10 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>1.88</v>
+        <v>2.97</v>
       </c>
       <c r="H116" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -6674,37 +6676,37 @@
         </is>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Derrick White</t>
+          <t>Collin Murray-Boyles</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6712,10 +6714,10 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>7.06</v>
+        <v>10.64</v>
       </c>
       <c r="H117" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -6732,33 +6734,33 @@
       </c>
       <c r="L117" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Egor Demin</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2.5</v>
+        <v>10.5</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6766,10 +6768,10 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>2.92</v>
+        <v>12.44</v>
       </c>
       <c r="H118" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -6782,9 +6784,9 @@
         </is>
       </c>
       <c r="K118" t="n">
-        <v>4</v>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -6793,26 +6795,26 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kyle Kuzma</t>
+          <t>Wendell Carter Jr.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>12.5</v>
+        <v>1.5</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6820,10 +6822,10 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>13.63</v>
+        <v>1.87</v>
       </c>
       <c r="H119" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -6836,9 +6838,9 @@
         </is>
       </c>
       <c r="K119" t="n">
-        <v>3</v>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -6874,10 +6876,10 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>12.28</v>
+        <v>12.67</v>
       </c>
       <c r="H120" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -6899,17 +6901,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Zaccharie Risacher</t>
+          <t>Bennedict Mathurin</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6918,7 +6920,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>13.5</v>
+        <v>32.5</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -6926,10 +6928,10 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>12.27</v>
+        <v>30.15</v>
       </c>
       <c r="H121" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -6941,38 +6943,36 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K121" t="n">
-        <v>8</v>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kawhi Leonard</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>28.5</v>
+        <v>4.5</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -6980,10 +6980,10 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>30.24</v>
+        <v>5.19</v>
       </c>
       <c r="H122" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.555</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -6995,27 +6995,29 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K122" t="n">
+        <v>2</v>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Nic Claxton</t>
+          <t>Tristan Vukcevic</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7024,7 +7026,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -7032,14 +7034,14 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>3.56</v>
+        <v>1.85</v>
       </c>
       <c r="H123" t="n">
-        <v>0.556</v>
+        <v>0.553</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -7047,38 +7049,36 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K123" t="n">
-        <v>5</v>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Isaiah Joe</t>
+          <t>Michael Porter Jr.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3.5</v>
+        <v>22.5</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -7086,10 +7086,10 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>3.41</v>
+        <v>20.44</v>
       </c>
       <c r="H124" t="n">
-        <v>0.556</v>
+        <v>0.55</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -7102,9 +7102,9 @@
         </is>
       </c>
       <c r="K124" t="n">
-        <v>2</v>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
+        <v>18</v>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -7113,26 +7113,26 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Evan Mobley</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>21.5</v>
+        <v>2.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -7140,10 +7140,10 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>22.55</v>
+        <v>2.87</v>
       </c>
       <c r="H125" t="n">
-        <v>0.556</v>
+        <v>0.548</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -7155,29 +7155,27 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K125" t="n">
-        <v>18</v>
-      </c>
-      <c r="L125" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tre Johnson</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -7186,7 +7184,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -7194,14 +7192,14 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1.64</v>
+        <v>3.05</v>
       </c>
       <c r="H126" t="n">
-        <v>0.555</v>
+        <v>0.545</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -7210,37 +7208,37 @@
         </is>
       </c>
       <c r="K126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Myles Turner</t>
+          <t>Nikola Jokic</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>7.5</v>
+        <v>29.5</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -7248,10 +7246,10 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>7.92</v>
+        <v>31.15</v>
       </c>
       <c r="H127" t="n">
-        <v>0.553</v>
+        <v>0.545</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -7264,37 +7262,37 @@
         </is>
       </c>
       <c r="K127" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Moses Moody</t>
+          <t>Corey Kispert</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1.5</v>
+        <v>8.5</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -7302,10 +7300,10 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1.85</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>0.551</v>
+        <v>0.545</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -7318,9 +7316,9 @@
         </is>
       </c>
       <c r="K128" t="n">
-        <v>5</v>
-      </c>
-      <c r="L128" s="3" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -7329,26 +7327,26 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -7356,10 +7354,10 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>19.49</v>
+        <v>5.22</v>
       </c>
       <c r="H129" t="n">
-        <v>0.549</v>
+        <v>0.544</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -7372,9 +7370,9 @@
         </is>
       </c>
       <c r="K129" t="n">
-        <v>25</v>
-      </c>
-      <c r="L129" s="3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -7383,26 +7381,26 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dominick Barlow</t>
+          <t>Nic Claxton</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -7410,14 +7408,14 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>9.33</v>
+        <v>9.9</v>
       </c>
       <c r="H130" t="n">
-        <v>0.548</v>
+        <v>0.544</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -7426,37 +7424,37 @@
         </is>
       </c>
       <c r="K130" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kris Dunn</t>
+          <t>Aaron Wiggins</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -7464,10 +7462,10 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>6.97</v>
+        <v>3.89</v>
       </c>
       <c r="H131" t="n">
-        <v>0.546</v>
+        <v>0.544</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -7479,36 +7477,38 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K131" t="n">
+        <v>3</v>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Aaron Wiggins</t>
+          <t>Austin Reaves</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>3.5</v>
+        <v>29.5</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -7516,14 +7516,14 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3.9</v>
+        <v>27.9</v>
       </c>
       <c r="H132" t="n">
-        <v>0.546</v>
+        <v>0.544</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -7532,37 +7532,37 @@
         </is>
       </c>
       <c r="K132" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Wendell Carter Jr.</t>
+          <t>Jared McCain</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1.5</v>
+        <v>11.5</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1.83</v>
+        <v>12.59</v>
       </c>
       <c r="H133" t="n">
-        <v>0.545</v>
+        <v>0.543</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -7586,9 +7586,9 @@
         </is>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
-      </c>
-      <c r="L133" s="2" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -7597,26 +7597,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Jonas Valanciunas</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -7624,14 +7624,14 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>7.93</v>
+        <v>3.48</v>
       </c>
       <c r="H134" t="n">
-        <v>0.544</v>
+        <v>0.541</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -7640,37 +7640,37 @@
         </is>
       </c>
       <c r="K134" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Noah Clowney</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1.5</v>
+        <v>4.5</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -7678,14 +7678,14 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1.82</v>
+        <v>4.96</v>
       </c>
       <c r="H135" t="n">
-        <v>0.543</v>
+        <v>0.54</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -7694,28 +7694,28 @@
         </is>
       </c>
       <c r="K135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sam Merrill</t>
+          <t>Kris Dunn</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H136" t="n">
-        <v>0.541</v>
+        <v>0.54</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -7747,34 +7747,32 @@
           <t>C Tier</t>
         </is>
       </c>
-      <c r="K136" t="n">
-        <v>20</v>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Quentin Grimes</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>PHI</t>
-        </is>
-      </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E137" t="n">
@@ -7786,25 +7784,27 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="H137" t="n">
-        <v>0.538</v>
+        <v>0.539</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+          <t>C Tier</t>
+        </is>
+      </c>
+      <c r="K137" t="n">
+        <v>1</v>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
@@ -7826,11 +7826,11 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>17.5</v>
+        <v>1.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -7838,25 +7838,25 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>18.22</v>
+        <v>1.73</v>
       </c>
       <c r="H138" t="n">
-        <v>0.538</v>
+        <v>0.539</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="K138" t="n">
-        <v>15</v>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -7865,26 +7865,26 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Kon Knueppel</t>
+          <t>Jonas Valanciunas</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -7892,25 +7892,25 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>5.46</v>
+        <v>8.02</v>
       </c>
       <c r="H139" t="n">
-        <v>0.537</v>
+        <v>0.538</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="K139" t="n">
-        <v>7</v>
-      </c>
-      <c r="L139" s="2" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -7919,26 +7919,26 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Pat Spencer</t>
+          <t>Zaccharie Risacher</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>9.5</v>
+        <v>13.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -7946,53 +7946,53 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>9.85</v>
+        <v>12.14</v>
       </c>
       <c r="H140" t="n">
-        <v>0.536</v>
+        <v>0.537</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>C Tier</t>
         </is>
       </c>
       <c r="K140" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Dennis Schroder</t>
+          <t>Nickeil Alexander-Walker</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>14.24</v>
+        <v>4.03</v>
       </c>
       <c r="H141" t="n">
-        <v>0.536</v>
+        <v>0.533</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -8016,9 +8016,9 @@
         </is>
       </c>
       <c r="K141" t="n">
-        <v>22</v>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -8027,17 +8027,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Luka Doncic</t>
+          <t>Kevin Porter Jr.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -8046,7 +8046,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>29.5</v>
+        <v>18.5</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -8054,10 +8054,10 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>30.65</v>
+        <v>19.56</v>
       </c>
       <c r="H142" t="n">
-        <v>0.535</v>
+        <v>0.532</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -8070,28 +8070,28 @@
         </is>
       </c>
       <c r="K142" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Kevin Porter Jr.</t>
+          <t>Kristaps Porzingis</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -8100,7 +8100,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -8108,14 +8108,14 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>17.79</v>
+        <v>13.45</v>
       </c>
       <c r="H143" t="n">
-        <v>0.535</v>
+        <v>0.531</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -8123,29 +8123,27 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K143" t="n">
-        <v>21</v>
-      </c>
-      <c r="L143" s="2" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>VJ Edgecombe</t>
+          <t>Julian Strawther</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -8154,7 +8152,7 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -8162,7 +8160,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>5.86</v>
+        <v>4.35</v>
       </c>
       <c r="H144" t="n">
         <v>0.531</v>
@@ -8178,9 +8176,9 @@
         </is>
       </c>
       <c r="K144" t="n">
-        <v>5</v>
-      </c>
-      <c r="L144" s="2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -8189,26 +8187,26 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Max Christie</t>
+          <t>Ryan Rollins</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -8216,10 +8214,10 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>3.53</v>
+        <v>9.15</v>
       </c>
       <c r="H145" t="n">
-        <v>0.531</v>
+        <v>0.53</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -8232,37 +8230,37 @@
         </is>
       </c>
       <c r="K145" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L145" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Kristaps Porzingis</t>
+          <t>AJ Green</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -8270,14 +8268,14 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>13.07</v>
+        <v>13.56</v>
       </c>
       <c r="H146" t="n">
-        <v>0.53</v>
+        <v>0.529</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -8285,36 +8283,38 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>Pending / Not Found</t>
+      <c r="K146" t="n">
+        <v>5</v>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Christian Braun</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -8322,14 +8322,14 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>7.23</v>
+        <v>13.37</v>
       </c>
       <c r="H147" t="n">
-        <v>0.528</v>
+        <v>0.529</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -8342,33 +8342,33 @@
       </c>
       <c r="L147" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Gui Santos</t>
+          <t>Rui Hachimura</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>11.5</v>
+        <v>2.5</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -8376,14 +8376,14 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>11.78</v>
+        <v>2.81</v>
       </c>
       <c r="H148" t="n">
-        <v>0.525</v>
+        <v>0.528</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -8392,9 +8392,9 @@
         </is>
       </c>
       <c r="K148" t="n">
-        <v>17</v>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -8403,26 +8403,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>Max Christie</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5.5</v>
+        <v>23.5</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -8430,14 +8430,14 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>5.71</v>
+        <v>22.83</v>
       </c>
       <c r="H149" t="n">
-        <v>0.523</v>
+        <v>0.526</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -8446,28 +8446,28 @@
         </is>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Cason Wallace</t>
+          <t>Daniel Gafford</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>11.5</v>
+        <v>7.5</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -8484,14 +8484,14 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>11.05</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H150" t="n">
-        <v>0.522</v>
+        <v>0.526</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -8500,37 +8500,37 @@
         </is>
       </c>
       <c r="K150" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Daniel Gafford</t>
+          <t>Jamal Murray</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>REB</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>7.79</v>
+        <v>5.22</v>
       </c>
       <c r="H151" t="n">
-        <v>0.521</v>
+        <v>0.524</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -8554,28 +8554,28 @@
         </is>
       </c>
       <c r="K151" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L151" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>James Harden</t>
+          <t>Marcus Smart</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>19.5</v>
+        <v>7.5</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -8592,10 +8592,10 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>19.18</v>
+        <v>7.02</v>
       </c>
       <c r="H152" t="n">
-        <v>0.519</v>
+        <v>0.523</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -8608,37 +8608,37 @@
         </is>
       </c>
       <c r="K152" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Corey Kispert</t>
+          <t>Tim Hardaway Jr.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>GSW</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>AST</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1.5</v>
+        <v>15.5</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -8646,10 +8646,10 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.74</v>
+        <v>16.49</v>
       </c>
       <c r="H153" t="n">
-        <v>0.517</v>
+        <v>0.523</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -8662,9 +8662,9 @@
         </is>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -8673,26 +8673,26 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Jamal Murray</t>
+          <t>Donte DiVincenzo</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>GSW</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>35.5</v>
+        <v>10.5</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -8700,10 +8700,10 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>35.99</v>
+        <v>11</v>
       </c>
       <c r="H154" t="n">
-        <v>0.515</v>
+        <v>0.522</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -8716,37 +8716,37 @@
         </is>
       </c>
       <c r="K154" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>LOSS</t>
+          <t>WIN</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Isaiah Hartenstein</t>
+          <t>Onyeka Okongwu</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>23.5</v>
+        <v>14.5</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -8754,10 +8754,10 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>23.77</v>
+        <v>14.98</v>
       </c>
       <c r="H155" t="n">
-        <v>0.514</v>
+        <v>0.52</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -8770,33 +8770,33 @@
         </is>
       </c>
       <c r="K155" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="L155" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dean Wade</t>
+          <t>Brandon Miller</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="E156" t="n">
@@ -8808,14 +8808,14 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>3.67</v>
+        <v>3.76</v>
       </c>
       <c r="H156" t="n">
-        <v>0.514</v>
+        <v>0.518</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -8828,24 +8828,24 @@
       </c>
       <c r="L156" s="3" t="inlineStr">
         <is>
-          <t>WIN</t>
+          <t>LOSS</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Marcus Smart</t>
+          <t>Jaylon Tyson</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -8854,7 +8854,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -8862,14 +8862,14 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>2.72</v>
+        <v>4.12</v>
       </c>
       <c r="H157" t="n">
-        <v>0.511</v>
+        <v>0.518</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Under</t>
+          <t>Over</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -8878,9 +8878,9 @@
         </is>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
@@ -8889,26 +8889,26 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Nikola Vucevic</t>
+          <t>Gui Santos</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>12.5</v>
+        <v>8.5</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -8916,14 +8916,14 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>12.67</v>
+        <v>8.31</v>
       </c>
       <c r="H158" t="n">
-        <v>0.51</v>
+        <v>0.517</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Over</t>
+          <t>Under</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -8932,9 +8932,9 @@
         </is>
       </c>
       <c r="K158" t="n">
-        <v>9</v>
-      </c>
-      <c r="L158" s="2" t="inlineStr">
+        <v>12</v>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -8943,26 +8943,26 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Cam Thomas</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>29.5</v>
+        <v>19.5</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -8970,10 +8970,10 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>29.7</v>
+        <v>20.2</v>
       </c>
       <c r="H159" t="n">
-        <v>0.507</v>
+        <v>0.515</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -8986,9 +8986,9 @@
         </is>
       </c>
       <c r="K159" t="n">
-        <v>28</v>
-      </c>
-      <c r="L159" s="2" t="inlineStr">
+        <v>19</v>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
         <is>
           <t>LOSS</t>
         </is>
@@ -8997,26 +8997,26 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Jaylon Tyson</t>
+          <t>Nikola Vucevic</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>REB</t>
+          <t>PTS</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -9024,25 +9024,563 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>3.68</v>
+        <v>12.84</v>
       </c>
       <c r="H160" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K160" t="n">
+        <v>9</v>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CJ McCollum</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K161" t="n">
+        <v>16</v>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Christian Braun</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K162" t="n">
+        <v>7</v>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Ayo Dosunmu</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>12.74</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>12</v>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Baylor Scheierman</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>12.23</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Under</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>9</v>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Kawhi Leonard</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>LAC</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>ORL</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>28.85</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Pending / Not Found</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Tre Johnson</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>WSH</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K166" t="n">
+        <v>11</v>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Naji Marshall</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K167" t="n">
+        <v>17</v>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="K168" t="n">
+        <v>27</v>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Sam Hauser</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="H169" t="n">
         <v>0.501</v>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I169" t="inlineStr">
         <is>
           <t>Over</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="J169" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="K160" t="n">
-        <v>4</v>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
+      <c r="K169" t="n">
+        <v>7</v>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Payton Pritchard</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>LAL</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Over</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Trap / High Variance</t>
+        </is>
+      </c>
+      <c r="K170" t="n">
+        <v>30</v>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
